--- a/Repo_Control_File.xlsx
+++ b/Repo_Control_File.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aprashar\Documents\Github\DWRAT_DataScraping\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aprashar\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C4C3512-4BDD-405E-9FC3-19B16AF592C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECACDD74-D817-4575-A3F4-615B03C5C85D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="30">
   <si>
     <t>VALUE</t>
   </si>
@@ -109,6 +109,12 @@
   </si>
   <si>
     <t>URL that points to "My Content" on ArcGIS Portal</t>
+  </si>
+  <si>
+    <t>TEST_FIELD</t>
+  </si>
+  <si>
+    <t>TEST</t>
   </si>
 </sst>
 </file>
@@ -437,7 +443,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
@@ -582,6 +588,17 @@
         <v>27</v>
       </c>
     </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" t="s">
+        <v>29</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
